--- a/Library/Library_Data/Data.xlsx
+++ b/Library/Library_Data/Data.xlsx
@@ -8,26 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\training\Python\Library\Library_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4641E51E-E0C9-4902-AA94-CAFDA055F824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B535A8-B990-4D4D-B981-A604C3A81F8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{5AC4A92E-3BC1-4762-B3C1-D3EEB6357069}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>Buyer Names</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>Renter Names</t>
   </si>
   <si>
     <t>Unique code Of Book</t>
@@ -45,13 +40,58 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>Total Cost</t>
+    <t>Charges/book/day</t>
+  </si>
+  <si>
+    <t>Issue Date</t>
+  </si>
+  <si>
+    <t>Rental Period</t>
+  </si>
+  <si>
+    <t>Due Date</t>
+  </si>
+  <si>
+    <t>Total Rent</t>
+  </si>
+  <si>
+    <t>Mayuresh Jagtap</t>
+  </si>
+  <si>
+    <t>MYTH10005</t>
+  </si>
+  <si>
+    <t>Shiva to Shankara</t>
+  </si>
+  <si>
+    <t>Devdutt Pattanaik</t>
+  </si>
+  <si>
+    <t>Manish Patel</t>
+  </si>
+  <si>
+    <t>NOV10009</t>
+  </si>
+  <si>
+    <t>The Lowland</t>
+  </si>
+  <si>
+    <t>Jhumpa Lahiri</t>
+  </si>
+  <si>
+    <t>31-08-2026</t>
+  </si>
+  <si>
+    <t>12-09-2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -105,11 +145,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -424,8 +467,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5414439-64FE-4C99-9475-1A381CEACBA1}">
-  <dimension ref="A1:G9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
@@ -434,56 +477,117 @@
     <col min="4" max="4" width="28.28515625" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" customWidth="1"/>
     <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="17.28515625" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2">
+        <v>275</v>
+      </c>
+      <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>11</v>
+      </c>
+      <c r="H2" s="2">
+        <v>46265</v>
+      </c>
+      <c r="I2" s="3">
+        <v>25</v>
+      </c>
+      <c r="J2" s="2">
+        <v>46290.613081284719</v>
+      </c>
+      <c r="K2">
+        <v>99</v>
+      </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <v>399</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Library/Library_Data/Data.xlsx
+++ b/Library/Library_Data/Data.xlsx
@@ -1,118 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\training\Python\Library\Library_Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B535A8-B990-4D4D-B981-A604C3A81F8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>Renter Names</t>
-  </si>
-  <si>
-    <t>Unique code Of Book</t>
-  </si>
-  <si>
-    <t>Name Of Book</t>
-  </si>
-  <si>
-    <t>Author Of Book</t>
-  </si>
-  <si>
-    <t>Price Of Book</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Charges/book/day</t>
-  </si>
-  <si>
-    <t>Issue Date</t>
-  </si>
-  <si>
-    <t>Rental Period</t>
-  </si>
-  <si>
-    <t>Due Date</t>
-  </si>
-  <si>
-    <t>Total Rent</t>
-  </si>
-  <si>
-    <t>Mayuresh Jagtap</t>
-  </si>
-  <si>
-    <t>MYTH10005</t>
-  </si>
-  <si>
-    <t>Shiva to Shankara</t>
-  </si>
-  <si>
-    <t>Devdutt Pattanaik</t>
-  </si>
-  <si>
-    <t>Manish Patel</t>
-  </si>
-  <si>
-    <t>NOV10009</t>
-  </si>
-  <si>
-    <t>The Lowland</t>
-  </si>
-  <si>
-    <t>Jhumpa Lahiri</t>
-  </si>
-  <si>
-    <t>31-08-2026</t>
-  </si>
-  <si>
-    <t>12-09-2026</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -146,28 +72,87 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -467,126 +452,219 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.140625" customWidth="1"/>
-    <col min="3" max="3" width="36.42578125" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col width="22.85546875" customWidth="1" min="1" max="1"/>
+    <col width="24.140625" customWidth="1" min="2" max="2"/>
+    <col width="36.42578125" customWidth="1" min="3" max="3"/>
+    <col width="28.28515625" customWidth="1" min="4" max="4"/>
+    <col width="18.5703125" customWidth="1" min="5" max="5"/>
+    <col width="14.7109375" customWidth="1" min="6" max="6"/>
+    <col width="18.5703125" customWidth="1" min="7" max="7"/>
+    <col width="18.28515625" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="14.85546875" customWidth="1" min="9" max="9"/>
+    <col width="13.85546875" customWidth="1" min="10" max="10"/>
+    <col width="10.85546875" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Renter Names</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unique code Of Book</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Name Of Book</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Author Of Book</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Price Of Book</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Charges/book/day</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Issue Date</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Rental Period</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Due Date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Total Rent</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mayuresh Jagtap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MYTH10005</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Shiva to Shankara</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Devdutt Pattanaik</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>275</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>46290.61308128472</v>
+      </c>
+      <c r="K2" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Manish Patel</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NOV10009</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>The Lowland</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Jhumpa Lahiri</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>399</v>
+      </c>
+      <c r="F3" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>12-09-2026</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aman Sharma</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NOV10007</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Clear Light of Day</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Anita Desai</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>320</v>
+      </c>
+      <c r="F4" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="G4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2">
-        <v>275</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>11</v>
-      </c>
-      <c r="H2" s="2">
-        <v>46265</v>
-      </c>
-      <c r="I2" s="3">
-        <v>25</v>
-      </c>
-      <c r="J2" s="2">
-        <v>46290.613081284719</v>
-      </c>
-      <c r="K2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3">
-        <v>399</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>16</v>
-      </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3">
-        <v>12</v>
-      </c>
-      <c r="J3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3">
-        <v>16</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>06-09-2026</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Library/Library_Data/Data.xlsx
+++ b/Library/Library_Data/Data.xlsx
@@ -15,9 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -71,14 +69,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -457,20 +451,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22.85546875" customWidth="1" min="1" max="1"/>
-    <col width="24.140625" customWidth="1" min="2" max="2"/>
-    <col width="36.42578125" customWidth="1" min="3" max="3"/>
-    <col width="28.28515625" customWidth="1" min="4" max="4"/>
-    <col width="18.5703125" customWidth="1" min="5" max="5"/>
-    <col width="14.7109375" customWidth="1" min="6" max="6"/>
-    <col width="18.5703125" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="18.42578125" customWidth="1" min="2" max="2"/>
+    <col width="24.140625" customWidth="1" min="3" max="3"/>
+    <col width="36.42578125" customWidth="1" min="4" max="4"/>
+    <col width="28.28515625" customWidth="1" min="5" max="5"/>
+    <col width="18.5703125" customWidth="1" min="6" max="7"/>
     <col width="18.28515625" bestFit="1" customWidth="1" min="8" max="8"/>
     <col width="14.85546875" customWidth="1" min="9" max="9"/>
     <col width="13.85546875" customWidth="1" min="10" max="10"/>
-    <col width="10.85546875" customWidth="1" min="11" max="11"/>
+    <col width="15.28515625" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,27 +474,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Phone Number</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Unique code Of Book</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Name Of Book</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Author Of Book</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Price Of Book</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Quantity</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -533,138 +526,99 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mayuresh Jagtap</t>
+          <t>Nitin Menon</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MYTH10005</t>
+          <t>8798000000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Shiva to Shankara</t>
+          <t>ROMNC10005</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Devdutt Pattanaik</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>275</v>
+          <t>The 3 Mistakes of My Life</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Chetan Bhagat</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>199</v>
       </c>
       <c r="G2" t="n">
-        <v>11</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>46265</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>46290.61308128472</v>
+        <v>8</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>01-09-2026</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>06-09-2026</t>
+        </is>
       </c>
       <c r="K2" t="n">
-        <v>99</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Manish Patel</t>
+          <t>Aman Patel</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NOV10009</t>
+          <t>7587120000</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The Lowland</t>
+          <t>NOV10010</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Jhumpa Lahiri</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>399</v>
+          <t>Sea of Poppies</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Amitav Ghosh</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>450</v>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>12-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Aman Sharma</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NOV10007</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Clear Light of Day</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Anita Desai</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>320</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>13</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>31-08-2026</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>6</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>06-09-2026</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>26</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/Library/Library_Data/Data.xlsx
+++ b/Library/Library_Data/Data.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -621,6 +621,104 @@
         <v>180</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Manik Parn</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>9878000000</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MYTH10001</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>The Palace of Illusions</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Chitra Banerjee Divakaruni</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>250</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>01-09-2026</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>03-09-2026</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ali Muhammad</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>7864388888</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NOV10005</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Midnight's Children</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Salman Rushdie</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>499</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>01-09-2026</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>08-09-2026</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>140</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Library/Library_Data/Data.xlsx
+++ b/Library/Library_Data/Data.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -583,6 +583,162 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Aman Mishra</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>9878987000</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>MYTH10003</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Asura: Tale of the Vanquished</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Anand Neelakantan</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>02-09-2026</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Farhan Sarod</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>7998789879</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>NOV10003</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>A Suitable Boy</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Vikram Seth</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>02-09-2026</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Aman Jha</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>5676567656</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>ROMNC10003</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Wish I Could Tell You</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Durjoy Datta</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>02-09-2026</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>NO</t>
         </is>
       </c>
@@ -598,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -676,59 +832,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Paresh Thakur</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>7877989898</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>MYTH10001</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>The Palace of Illusions</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Chitra Banerjee Divakaruni</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>250</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>02-09-2026</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>05-09-2026</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Library/Library_Data/Data.xlsx
+++ b/Library/Library_Data/Data.xlsx
@@ -1,122 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\training\Python\Library\Library_Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82137E44-3FB3-4111-B599-3C90378F858C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="23">
-  <si>
-    <t>Buyer Names</t>
-  </si>
-  <si>
-    <t>Phone Numbers</t>
-  </si>
-  <si>
-    <t>Unique code Of Book</t>
-  </si>
-  <si>
-    <t>Name Of Book</t>
-  </si>
-  <si>
-    <t>Author Of Book</t>
-  </si>
-  <si>
-    <t>Price Of Book</t>
-  </si>
-  <si>
-    <t>Charges/book/day</t>
-  </si>
-  <si>
-    <t>Issue Date</t>
-  </si>
-  <si>
-    <t>Rental/Period</t>
-  </si>
-  <si>
-    <t>Due Date</t>
-  </si>
-  <si>
-    <t>Total Rent</t>
-  </si>
-  <si>
-    <t>Return</t>
-  </si>
-  <si>
-    <t>Salman Sarod</t>
-  </si>
-  <si>
-    <t>MYTH10001</t>
-  </si>
-  <si>
-    <t>The Palace of Illusions</t>
-  </si>
-  <si>
-    <t>Chitra Banerjee Divakaruni</t>
-  </si>
-  <si>
-    <t>03-09-2026</t>
-  </si>
-  <si>
-    <t>06-09-2026</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>NOV10001</t>
-  </si>
-  <si>
-    <t>The God of Small Things</t>
-  </si>
-  <si>
-    <t>Arundhati Roy</t>
-  </si>
-  <si>
-    <t>05-09-2026</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -150,30 +71,89 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -473,134 +453,502 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" customWidth="1"/>
-    <col min="4" max="4" width="43.140625" customWidth="1"/>
-    <col min="5" max="5" width="34.5703125" customWidth="1"/>
-    <col min="6" max="6" width="22.140625" customWidth="1"/>
-    <col min="7" max="7" width="20.140625" customWidth="1"/>
-    <col min="8" max="10" width="18.42578125" customWidth="1"/>
-    <col min="11" max="11" width="17.28515625" customWidth="1"/>
-    <col min="12" max="12" width="10.85546875" customWidth="1"/>
+    <col width="22.85546875" customWidth="1" min="1" max="1"/>
+    <col width="24.42578125" customWidth="1" min="2" max="2"/>
+    <col width="24.140625" customWidth="1" min="3" max="3"/>
+    <col width="43.140625" customWidth="1" min="4" max="4"/>
+    <col width="34.5703125" customWidth="1" min="5" max="5"/>
+    <col width="22.140625" customWidth="1" min="6" max="6"/>
+    <col width="20.140625" customWidth="1" min="7" max="7"/>
+    <col width="18.42578125" customWidth="1" min="8" max="10"/>
+    <col width="17.28515625" customWidth="1" min="11" max="11"/>
+    <col width="10.85546875" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Buyer Names</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Phone Numbers</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unique code Of Book</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Name Of Book</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Author Of Book</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Price Of Book</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Charges/book/day</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Issue Date</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Rental/Period</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Due Date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Total Rent</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Return</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Salman Sarod</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>9878987898</v>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>MYTH10001</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>The Palace of Illusions</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Chitra Banerjee Divakaruni</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>03-09-2026</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>06-09-2026</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Salman Sarod</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>9878987898</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>NOV10001</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>The God of Small Things</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Arundhati Roy</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>325</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>03-09-2026</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>05-09-2026</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Rakesh Sharma</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>9889988998</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>MYTH10002</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>The Immortals of Meluha</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Amish Tripathi</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>07-09-2026</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Nagesh Bhopi</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>8789878987</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>ROMNC10002</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>I Too Had a Love Story</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Ravinder Singh</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>07-09-2026</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Nagesh Bhopi</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>8789878987</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>MYTH10003</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Asura: Tale of the Vanquished</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Anand Neelakantan</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>06-09-2026</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Nagesh Bhopi</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>8789878987</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>NOV10009</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>The Lowland</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Jhumpa Lahiri</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>399</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>05-09-2026</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Nagesh Bhopi</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>8789878987</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>NOV10001</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>The God of Small Things</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Arundhati Roy</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>325</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>06-09-2026</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Santosh Patil</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>9898989898</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>MYTH10001</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>The Palace of Illusions</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Chitra Banerjee Divakaruni</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="G9" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="2">
-        <v>9878987898</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>06-09-2026</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="2">
-        <v>250</v>
-      </c>
-      <c r="G2" s="2">
-        <v>7</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2">
-        <v>3</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="2">
-        <v>21</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3">
-        <v>9878987898</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="2">
-        <v>325</v>
-      </c>
-      <c r="G3" s="2">
-        <v>9</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="2">
-        <v>2</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="2">
-        <v>18</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>18</v>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -609,58 +957,86 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" customWidth="1"/>
-    <col min="4" max="4" width="43.140625" customWidth="1"/>
-    <col min="5" max="5" width="34.5703125" customWidth="1"/>
-    <col min="6" max="6" width="22.140625" customWidth="1"/>
-    <col min="7" max="7" width="20.140625" customWidth="1"/>
-    <col min="8" max="10" width="18.42578125" customWidth="1"/>
-    <col min="11" max="11" width="17.28515625" customWidth="1"/>
-    <col min="12" max="12" width="10.85546875" customWidth="1"/>
+    <col width="22.85546875" customWidth="1" min="1" max="1"/>
+    <col width="24.42578125" customWidth="1" min="2" max="2"/>
+    <col width="24.140625" customWidth="1" min="3" max="3"/>
+    <col width="43.140625" customWidth="1" min="4" max="4"/>
+    <col width="34.5703125" customWidth="1" min="5" max="5"/>
+    <col width="22.140625" customWidth="1" min="6" max="6"/>
+    <col width="20.140625" customWidth="1" min="7" max="7"/>
+    <col width="18.42578125" customWidth="1" min="8" max="10"/>
+    <col width="17.28515625" customWidth="1" min="11" max="11"/>
+    <col width="10.85546875" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Buyer Names</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Phone Numbers</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unique code Of Book</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Name Of Book</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Author Of Book</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Price Of Book</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Charges/book/day</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Issue Date</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Rental/Period</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Due Date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Total Rent</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Return</t>
+        </is>
       </c>
     </row>
   </sheetData>
